--- a/AAII_Financials/Quarterly/CDEVY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CDEVY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
   <si>
     <t>CDEVY</t>
   </si>
@@ -656,139 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -831,56 +839,62 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>768900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>803200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>708900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>662800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>608900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>547200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>594600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>753900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>959200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>763500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>979100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>636900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>629700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>574000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>854700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>675800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -923,56 +937,62 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>484900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>469000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>390200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>332300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>308600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>288900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>229500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>380400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>533400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>496300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>631200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>321800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>321700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>304900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>466700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>360900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1015,56 +1035,62 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>284000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>334300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>318700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>330500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>300200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>258200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>365100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>373400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>425800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>267200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>347900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>315200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>308000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>269000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>388000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>315000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1325,15 +1365,15 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>213800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1346,11 +1386,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1373,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1429,11 +1475,11 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1465,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,8 +1548,10 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1540,56 +1594,62 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>1447000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>757100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>632200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>567100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>486800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>361400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>492300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>554200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>700400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>635000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>816600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>466500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>479700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>475500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>619100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>496200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1632,56 +1692,62 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>-678200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>46200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>76700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>95700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>122000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>185700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>102300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>199700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>258800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>128400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>162400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>170400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>150000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>98400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>235600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>179600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,56 +1826,62 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>-591700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>41600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>40400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>58500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>71500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>37000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>3500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>16700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>40700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>40700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>31500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>13600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>7200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>16500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1850,56 +1924,62 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>-1161000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>193000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>175400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>204200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>241700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>269600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>150900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>250000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>300500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>181300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>242300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>251700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>221600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>150700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>290500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>234000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1942,56 +2022,62 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>70100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>77500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>36000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>37700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>32700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>27900</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>23800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>21300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>20300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>43100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>40200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>42100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>20300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2034,56 +2120,62 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>-1339900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>81100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>116400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>160800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>194800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>105800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>185800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>240800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>124900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>160000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>171000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>139500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>91700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>242800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,56 +2218,62 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>55200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>10000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>23400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>30000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>39700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>28000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>38300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>64200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>24400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>14900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>28700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>23100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>11400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>46700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,8 +2364,14 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2310,56 +2414,62 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>-1395100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>71000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>93100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>130800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>155100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>77800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>147500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>176600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>100500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>145100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>142300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>116400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>80400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>196100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2402,56 +2512,62 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>-1430800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>60800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>86100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>111700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>146300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>73800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>128500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>151200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>61600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>112800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>108100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>79400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>70000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>173800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2586,11 +2708,11 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2634,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2862,56 +3002,62 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>591700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-41600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-40400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-58500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-71500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-37000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-3500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-40700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-13600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2954,56 +3100,62 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>-1430800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>60800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>86100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>111700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>146300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>73800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>128500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>151200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>61600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>112800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>108100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>79400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>70000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>173800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,8 +3246,14 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3138,153 +3296,165 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>-1430800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>60800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>86100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>111700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>146300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>73800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>128500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>151200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>61600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>112800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>108100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>79400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>70000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>173800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,755 +3523,805 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1558400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1564700</v>
+      </c>
+      <c r="F41" s="3">
         <v>1601500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1595800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1501500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1422900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2199200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2340200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1402900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1410600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1818600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1757900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1459600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1485500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1762400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2321400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1798100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2094500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2042800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2121800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1595400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1726800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1939200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1913400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2459600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2784200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2582400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2429900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2567300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2690100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2103600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F42" s="3">
         <v>43200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>43000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>35600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>33800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>140300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>149300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>30900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>31100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>14700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>14200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>26200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>26700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>9700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>14900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>15100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>421300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>16200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>13100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>10600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>10700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>10900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>11100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>11200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>11600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>12100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>13000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>13000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>12000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1367300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1372800</v>
+      </c>
+      <c r="F43" s="3">
         <v>1176500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1172300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1093700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1036400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1218600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1296700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1788800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1798600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1984900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1918700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1655000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1684400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1435400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1623400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1020800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>796700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1287600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1226000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1285200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>801600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>794300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>769900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1003900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>888100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>711700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>896000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>851100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>854300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1019200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5660000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5682900</v>
+      </c>
+      <c r="F44" s="3">
         <v>5560500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5540700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4645000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4401900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3560600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3788800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3663100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3683200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3702400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3578900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3755300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3822000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>4449200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4010700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>4206800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3872300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>4069200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3958100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4135700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4312600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>4355700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>4108500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3150600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3184500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3730100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3830700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3812300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3823600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>4508500</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>94600</v>
+      </c>
+      <c r="F45" s="3">
         <v>173900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>173300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>354700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>336100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>126700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>134800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>38200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>38400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>42500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>41100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>59800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>60900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>158600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>57600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>141600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>177800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>12300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>8400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>12000</v>
-      </c>
-      <c r="X45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>3600</v>
       </c>
       <c r="Z45" s="3">
         <v>2800</v>
       </c>
       <c r="AA45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AC45" s="3">
         <v>54000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>220900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>2800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>202000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8773100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8808700</v>
+      </c>
+      <c r="F46" s="3">
         <v>8613600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8582800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7695700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7292900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7306500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7774800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7004000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7042500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7648800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7393600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7042900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>7167800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7890200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>8028000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>7182300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7362600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7428100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7327400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7031500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>6863700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>7102900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>6806400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>6627900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>6922300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7257200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>7172400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>7246600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>7382900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>7845000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2334900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2344400</v>
+      </c>
+      <c r="F47" s="3">
         <v>2328600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2320300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2282700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2163200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2379800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2532300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2340200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2353100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2371300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2292200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2205500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2244600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2225600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1877900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2762000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2108000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2181400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2063200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1874900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1976300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1775300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1688600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1693800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1426600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1393500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1370100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>1368200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>1362300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>1175600</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4278200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4295500</v>
+      </c>
+      <c r="F48" s="3">
         <v>4292000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4276700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3862500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3660400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3429100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3648800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3395200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3413900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3192000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3085500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2992500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3045600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3028500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7495100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>7395800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>7391300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>7087000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6767100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6705900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6603800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5797800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5281400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5399800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5491600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5573600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5511600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5411500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>5479600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>5451000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1400</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1500</v>
       </c>
       <c r="G49" s="3">
         <v>1400</v>
@@ -4108,35 +4330,35 @@
         <v>1500</v>
       </c>
       <c r="I49" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K49" s="3">
         <v>1600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4149,11 +4371,11 @@
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4179,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5736700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5760000</v>
+      </c>
+      <c r="F52" s="3">
         <v>5770900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5750300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6346700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>6014500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5620200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>5980300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5221200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>5249900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5124800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4953900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4579100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4660400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3958100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>179100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>520000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>507400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>505900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>447300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>184200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>310700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>457900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>526300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>425900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>437700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>423100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>271400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>271000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>274600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>112600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21142600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21228400</v>
+      </c>
+      <c r="F54" s="3">
         <v>21029700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20954600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20216700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19158500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18763100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19965400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17989500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18088500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>18359900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17747400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16841300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17140100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17139000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>17580000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17860100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>17369300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>17202300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>16604900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>15796500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>15754500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>15133700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>14302800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>14147400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>14278300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>14647400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>14325500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>14297200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>14499400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>14584200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>166900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>167600</v>
+      </c>
+      <c r="F57" s="3">
         <v>175900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>175300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>174200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>165100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>163000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>173400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>160800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>161700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>182500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>176400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>165900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>168800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>189900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1001500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>805400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>897600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1023500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>910200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>941300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>975600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1021000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1031300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1036700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>958000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1424300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1202900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1124800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1153700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1301500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2766000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2777200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2498500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2489600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3753500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3557100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3386800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3603800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2215800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2228000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2981200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2881700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2475000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2518900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2088500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1358800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1539100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1173600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1433200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1009800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>949200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>858500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>695900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>727400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>933500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1274000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>912100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1063400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1305700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1361200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>420300</v>
+      </c>
+      <c r="F59" s="3">
         <v>650600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>648300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>639900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>606400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>586200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>623800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>618000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>621400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>675600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>653000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>692800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>705100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1170900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>655500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>412100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>391200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>359800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>365600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>441900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>416400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>285100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>311000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>295600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>554500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>249700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>195000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>204500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>220700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>193400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3881900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3897600</v>
+      </c>
+      <c r="F60" s="3">
         <v>3860700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3846900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5063100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4798100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4619000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4915000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3471500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3490600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4323600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4179400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3823300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3891200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3667600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3745500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2576300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2827900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2556900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2709000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2393000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2341200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2164500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2038200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2059700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2446100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2948000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2310000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2392700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2680100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2856100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8454700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8489000</v>
+      </c>
+      <c r="F61" s="3">
         <v>8428300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8398200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6761900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6408000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6854400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7293600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7211500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7251200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6335000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6123700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5632800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5732700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5957400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6678000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6618800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5886500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5109600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4783300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4042600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3823500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>3325200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3117600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2754000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2769200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2552800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3033500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>3021400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2896600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>3059300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>474500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>476400</v>
+      </c>
+      <c r="F62" s="3">
         <v>141700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>141200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>417100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>395200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>130800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>139200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>150200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>151000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>156900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>151700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>79000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>80400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>78400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>294000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>211800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>220000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>221300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>217300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>218200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>331200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>445500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>406900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>449400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>475700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>526900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>565200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>552700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>567200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>505200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13201900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13255500</v>
+      </c>
+      <c r="F66" s="3">
         <v>12771900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12726300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12591300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11932300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11942000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12707300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11136600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11197900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11132800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10761400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9852100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10026900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10005700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11267100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9945300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9493100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9502400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9276700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8270000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>8180600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>7596300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7161600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6881800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7353600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>7685900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>7452300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>7483300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>7692700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>7983600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,56 +6175,62 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>186600</v>
+      </c>
+      <c r="E70" s="3">
+        <v>187300</v>
+      </c>
+      <c r="F70" s="3">
         <v>202400</v>
       </c>
-      <c r="E70" s="3">
+      <c r="G70" s="3">
         <v>201600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>204400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>193700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>206000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>219200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>207400</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>208600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="N70" s="3">
         <v>230600</v>
       </c>
-      <c r="M70" s="3">
+      <c r="O70" s="3">
         <v>222900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="P70" s="3">
         <v>244000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="Q70" s="3">
         <v>248300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>246300</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -5920,25 +6256,31 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>243500</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>241800</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6208600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6233800</v>
+      </c>
+      <c r="F72" s="3">
         <v>6189300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6167200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5855000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5548500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5451900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5801200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5424900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5454700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5560900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5375300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5253900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>5347100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>5366500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4900200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6494700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6481100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6333900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>5972500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6138000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>6177700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6134700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>5772500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5853300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5513500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5891100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5797600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5763200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5689000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>5562200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7225900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7255200</v>
+      </c>
+      <c r="F76" s="3">
         <v>7254800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7228900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6884400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6524100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6453300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6866800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6465000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6500600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6724600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6500200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6458700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6573200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6627200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6312900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7914800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7876200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>7699900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7328300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>7526500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7573900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>7537400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7141200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>7265600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6681200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>6961500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>6873200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>6813900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>6564800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6600600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,105 +6959,117 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6722,56 +7112,62 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>-1430800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>60800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>86100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>111700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>146300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>73800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>128500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>151200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>61600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>112800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>108100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>79400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>70000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>173800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F83" s="3">
         <v>51900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>55200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>49800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>50100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>45700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>44200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>49100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>50000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>51600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>48200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>49600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>51000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>52200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>108800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>105200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>58300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>50100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>48200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>46900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>45100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>40400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>38400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>36100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>39300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>40700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>40100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>38900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>47700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>37900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-371800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-370400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-218200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-206700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>180600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>192200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>161100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>162000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>172300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>166600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>183000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>186300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>126100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-393700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>204500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>112800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>142400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>156700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>209400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>149400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-735200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>370200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>122000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>223700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>85400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>302800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-59500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-59300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-139200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-131900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-44400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-47200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-24100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-24200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-79300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-76700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-25900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-26400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-220600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-47000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-53600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-70100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-31000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-38200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-52200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-32900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-38800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F94" s="3">
         <v>278500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>277500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-125500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-118900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-99600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-106000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-262300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-263700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-427800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-413500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-270000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-274800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>37800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-464600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-337100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>3500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-87300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-448400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-448700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-957200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-287900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-23500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>80000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-82100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>647800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-330600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,16 +8350,18 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>88300</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
@@ -7928,56 +8396,62 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S96" s="3">
         <v>-110800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-30700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-5300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-61700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-104500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-24400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-7900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-67100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-105900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-99900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-46800</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="F100" s="3">
         <v>224100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>223300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-60900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-57700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>328400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>349500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-75300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-75700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>295000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>285200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-19500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-19900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>81900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>740700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>423800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-160700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-196100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>974300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>194400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>488300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>4800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>382900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-215700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-122300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-289900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-234600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-468700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-305800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-10100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-9400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-12300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>16000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>9400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2400</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>2900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>7300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>5200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-17500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>15600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-111700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-112200</v>
+      </c>
+      <c r="F102" s="3">
         <v>125500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>125100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-401900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-380900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>407700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>433800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-179700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-180700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>35400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>34200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-109900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-111800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>73900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>418100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-297600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>47000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-174000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>665800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-97600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-255500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-150000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-379200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-258500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>202800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>171400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-144400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-204600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>497500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-243500</v>
       </c>
     </row>
